--- a/safe_drawer_log.xlsx
+++ b/safe_drawer_log.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Jul 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Five Guys 2065 — Safe &amp; Drawer Count Log — May 2026</t>
+          <t>Five Guys 2065 — Safe &amp; Drawer Count Log — July 2026</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Fri 05/01</t>
+          <t>Wed 07/01</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -605,101 +605,101 @@
       <c r="K4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Sat 05/02</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="6" t="n"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Thu 07/02</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Sun 05/03</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="6" t="n"/>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Fri 07/03</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Mon 05/04</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="4" t="n"/>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Sat 07/04</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Tue 05/05</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="4" t="n"/>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Sun 07/05</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Wed 05/06</t>
+          <t>Mon 07/06</t>
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
@@ -722,7 +722,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Thu 05/07</t>
+          <t>Tue 07/07</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -745,7 +745,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Fri 05/08</t>
+          <t>Wed 07/08</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -766,101 +766,101 @@
       <c r="K11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Sat 05/09</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="6" t="n"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Thu 07/09</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Sun 05/10</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="6" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Fri 07/10</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Mon 05/11</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="4" t="n"/>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Sat 07/11</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Tue 05/12</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="4" t="n"/>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Sun 07/12</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Wed 05/13</t>
+          <t>Mon 07/13</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -883,7 +883,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Thu 05/14</t>
+          <t>Tue 07/14</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -906,7 +906,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Fri 05/15</t>
+          <t>Wed 07/15</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -927,101 +927,101 @@
       <c r="K18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Sat 05/16</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="6" t="n"/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Thu 07/16</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Sun 05/17</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="6" t="n"/>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Fri 07/17</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Mon 05/18</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="4" t="n"/>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Sat 07/18</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="7" t="n"/>
+      <c r="K21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Tue 05/19</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="4" t="n"/>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Sun 07/19</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="7" t="n"/>
+      <c r="K22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Wed 05/20</t>
+          <t>Mon 07/20</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1044,7 +1044,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Thu 05/21</t>
+          <t>Tue 07/21</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1067,7 +1067,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Fri 05/22</t>
+          <t>Wed 07/22</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1088,101 +1088,101 @@
       <c r="K25" s="4" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Sat 05/23</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="7" t="n"/>
-      <c r="J26" s="7" t="n"/>
-      <c r="K26" s="6" t="n"/>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Thu 07/23</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Sun 05/24</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="6" t="n"/>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Fri 07/24</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Mon 05/25</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="4" t="n"/>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Sat 07/25</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="7" t="n"/>
+      <c r="K28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Tue 05/26</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="4" t="n"/>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Sun 07/26</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="7" t="n"/>
+      <c r="K29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Wed 05/27</t>
+          <t>Mon 07/27</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1205,7 +1205,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Thu 05/28</t>
+          <t>Tue 07/28</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1228,7 +1228,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Fri 05/29</t>
+          <t>Wed 07/29</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1249,50 +1249,50 @@
       <c r="K32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Sat 05/30</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E33" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="7" t="n"/>
-      <c r="J33" s="7" t="n"/>
-      <c r="K33" s="6" t="n"/>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Thu 07/30</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Sun 05/31</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="6" t="n"/>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="7" t="n"/>
-      <c r="K34" s="6" t="n"/>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Fri 07/31</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">

--- a/safe_drawer_log.xlsx
+++ b/safe_drawer_log.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Jul 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aug 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67,14 +67,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFF9E6"/>
+        <bgColor rgb="00FFF9E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9E6"/>
-        <bgColor rgb="00FFF9E6"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -513,7 +513,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Five Guys 2065 — Safe &amp; Drawer Count Log — July 2026</t>
+          <t>Five Guys 2065 — Safe &amp; Drawer Count Log — August 2026</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Wed 07/01</t>
+          <t>Sat 08/01</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Thu 07/02</t>
+          <t>Sun 08/02</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
@@ -628,32 +628,32 @@
       <c r="K5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Fri 07/03</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="4" t="n"/>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Mon 08/03</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Sat 07/04</t>
+          <t>Tue 08/04</t>
         </is>
       </c>
       <c r="B7" s="6" t="n"/>
@@ -676,7 +676,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Sun 07/05</t>
+          <t>Wed 08/05</t>
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
@@ -697,55 +697,55 @@
       <c r="K8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Mon 07/06</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="4" t="n"/>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Thu 08/06</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Tue 07/07</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="4" t="n"/>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Fri 08/07</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Wed 07/08</t>
+          <t>Sat 08/08</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -768,7 +768,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Thu 07/09</t>
+          <t>Sun 08/09</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -789,32 +789,32 @@
       <c r="K12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Fri 07/10</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="4" t="n"/>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Mon 08/10</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Sat 07/11</t>
+          <t>Tue 08/11</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
@@ -837,7 +837,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Sun 07/12</t>
+          <t>Wed 08/12</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
@@ -858,55 +858,55 @@
       <c r="K15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Mon 07/13</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="4" t="n"/>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Thu 08/13</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Tue 07/14</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="4" t="n"/>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Fri 08/14</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Wed 07/15</t>
+          <t>Sat 08/15</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -929,7 +929,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Thu 07/16</t>
+          <t>Sun 08/16</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -950,32 +950,32 @@
       <c r="K19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Fri 07/17</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="4" t="n"/>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Mon 08/17</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Sat 07/18</t>
+          <t>Tue 08/18</t>
         </is>
       </c>
       <c r="B21" s="6" t="n"/>
@@ -998,7 +998,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Sun 07/19</t>
+          <t>Wed 08/19</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
@@ -1019,55 +1019,55 @@
       <c r="K22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Mon 07/20</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="4" t="n"/>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Thu 08/20</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="7" t="n"/>
+      <c r="K23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Tue 07/21</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="4" t="n"/>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Fri 08/21</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="7" t="n"/>
+      <c r="K24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Wed 07/22</t>
+          <t>Sat 08/22</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1090,7 +1090,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Thu 07/23</t>
+          <t>Sun 08/23</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1111,32 +1111,32 @@
       <c r="K26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Fri 07/24</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="4" t="n"/>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Mon 08/24</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="7" t="n"/>
+      <c r="K27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Sat 07/25</t>
+          <t>Tue 08/25</t>
         </is>
       </c>
       <c r="B28" s="6" t="n"/>
@@ -1159,7 +1159,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Sun 07/26</t>
+          <t>Wed 08/26</t>
         </is>
       </c>
       <c r="B29" s="6" t="n"/>
@@ -1180,55 +1180,55 @@
       <c r="K29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Mon 07/27</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="4" t="n"/>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Thu 08/27</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="7" t="n"/>
+      <c r="K30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Tue 07/28</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="4" t="n"/>
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Fri 08/28</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="7" t="n"/>
+      <c r="K31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Wed 07/29</t>
+          <t>Sat 08/29</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1251,7 +1251,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Thu 07/30</t>
+          <t>Sun 08/30</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1272,27 +1272,27 @@
       <c r="K33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Fri 07/31</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="4" t="n"/>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Mon 08/31</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="7" t="n"/>
+      <c r="K34" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">

--- a/safe_drawer_log.xlsx
+++ b/safe_drawer_log.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Aug 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sep 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67,14 +67,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9E6"/>
-        <bgColor rgb="00FFF9E6"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFF9E6"/>
+        <bgColor rgb="00FFF9E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Five Guys 2065 — Safe &amp; Drawer Count Log — August 2026</t>
+          <t>Five Guys 2065 — Safe &amp; Drawer Count Log — September 2026</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Sat 08/01</t>
+          <t>Tue 09/01</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Sun 08/02</t>
+          <t>Wed 09/02</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
@@ -628,55 +628,55 @@
       <c r="K5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Mon 08/03</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="6" t="n"/>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Thu 09/03</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Tue 08/04</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="6" t="n"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Fri 09/04</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Wed 08/05</t>
+          <t>Sat 09/05</t>
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
@@ -699,7 +699,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Thu 08/06</t>
+          <t>Sun 09/06</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
@@ -720,32 +720,32 @@
       <c r="K9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Fri 08/07</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="6" t="n"/>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Mon 09/07</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Sat 08/08</t>
+          <t>Tue 09/08</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -768,7 +768,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Sun 08/09</t>
+          <t>Wed 09/09</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -789,55 +789,55 @@
       <c r="K12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Mon 08/10</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="6" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Thu 09/10</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Tue 08/11</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="6" t="n"/>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Fri 09/11</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Wed 08/12</t>
+          <t>Sat 09/12</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
@@ -860,7 +860,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Thu 08/13</t>
+          <t>Sun 09/13</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
@@ -881,32 +881,32 @@
       <c r="K16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Fri 08/14</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="6" t="n"/>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Mon 09/14</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Sat 08/15</t>
+          <t>Tue 09/15</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -929,7 +929,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Sun 08/16</t>
+          <t>Wed 09/16</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -950,55 +950,55 @@
       <c r="K19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Mon 08/17</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="6" t="n"/>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Thu 09/17</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Tue 08/18</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="6" t="n"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Fri 09/18</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Wed 08/19</t>
+          <t>Sat 09/19</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
@@ -1021,7 +1021,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Thu 08/20</t>
+          <t>Sun 09/20</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
@@ -1042,32 +1042,32 @@
       <c r="K23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Fri 08/21</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="7" t="n"/>
-      <c r="J24" s="7" t="n"/>
-      <c r="K24" s="6" t="n"/>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Mon 09/21</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Sat 08/22</t>
+          <t>Tue 09/22</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1090,7 +1090,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Sun 08/23</t>
+          <t>Wed 09/23</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1111,55 +1111,55 @@
       <c r="K26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Mon 08/24</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="6" t="n"/>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Thu 09/24</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Tue 08/25</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
-      <c r="K28" s="6" t="n"/>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Fri 09/25</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Wed 08/26</t>
+          <t>Sat 09/26</t>
         </is>
       </c>
       <c r="B29" s="6" t="n"/>
@@ -1182,7 +1182,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Thu 08/27</t>
+          <t>Sun 09/27</t>
         </is>
       </c>
       <c r="B30" s="6" t="n"/>
@@ -1203,32 +1203,32 @@
       <c r="K30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Fri 08/28</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="7" t="n"/>
-      <c r="J31" s="7" t="n"/>
-      <c r="K31" s="6" t="n"/>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Mon 09/28</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Sat 08/29</t>
+          <t>Tue 09/29</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1251,7 +1251,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Sun 08/30</t>
+          <t>Wed 09/30</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1271,41 +1271,18 @@
       <c r="J33" s="5" t="n"/>
       <c r="K33" s="4" t="n"/>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Mon 08/31</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="6" t="n"/>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="7" t="n"/>
-      <c r="K34" s="6" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>MONTH TOTALS</t>
         </is>
       </c>
-      <c r="I36" s="9">
-        <f>SUM(I4:I34)</f>
+      <c r="I35" s="9">
+        <f>SUM(I4:I33)</f>
         <v/>
       </c>
-      <c r="J36" s="9">
-        <f>SUM(J4:J34)</f>
+      <c r="J35" s="9">
+        <f>SUM(J4:J33)</f>
         <v/>
       </c>
     </row>
